--- a/walla-walla-wineries.xlsx
+++ b/walla-walla-wineries.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:Q92"/>
   <cols>
     <col min="1" max="1" width="35.83203125" customWidth="1"/>
     <col min="2" max="2" width="30.83203125" customWidth="1"/>
@@ -408,9 +408,14 @@
     <col min="7" max="7" width="40.83203125" customWidth="1"/>
     <col min="8" max="8" width="50.83203125" customWidth="1"/>
     <col min="9" max="9" width="35.83203125" customWidth="1"/>
-    <col min="10" max="10" width="12.83203125" customWidth="1"/>
-    <col min="11" max="11" width="12.83203125" customWidth="1"/>
-    <col min="12" max="12" width="50.83203125" customWidth="1"/>
+    <col min="10" max="10" width="45.83203125" customWidth="1"/>
+    <col min="11" max="11" width="30.83203125" customWidth="1"/>
+    <col min="12" max="12" width="25.83203125" customWidth="1"/>
+    <col min="13" max="13" width="25.83203125" customWidth="1"/>
+    <col min="14" max="14" width="50.83203125" customWidth="1"/>
+    <col min="15" max="15" width="12.83203125" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="17" max="17" width="50.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -442,12 +447,27 @@
         <v>Region/District</v>
       </c>
       <c r="J1" t="str">
+        <v>Wine Varietals</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Hours of Operation</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Days Open</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Visit Type</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Photo URL</v>
+      </c>
+      <c r="O1" t="str">
         <v>Latitude</v>
       </c>
-      <c r="K1" t="str">
+      <c r="P1" t="str">
         <v>Longitude</v>
       </c>
-      <c r="L1" t="str">
+      <c r="Q1" t="str">
         <v>Notes</v>
       </c>
     </row>
@@ -480,12 +500,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J2" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah, Chardonnay</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L2" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M2" t="str">
+        <v>By Appointment</v>
+      </c>
+      <c r="N2" t="str">
+        <v>https://www.abeja.net/images/Abeja-Snow-Vineyard.jpg</v>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
         <v/>
       </c>
     </row>
@@ -518,12 +553,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L3" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M3" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N3" t="str">
+        <v/>
+      </c>
+      <c r="O3" t="str">
+        <v/>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
         <v/>
       </c>
     </row>
@@ -556,12 +606,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J4" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K4" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L4" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M4" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N4" t="str">
+        <v/>
+      </c>
+      <c r="O4" t="str">
+        <v/>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
         <v/>
       </c>
     </row>
@@ -594,12 +659,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J5" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K5" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L5" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M5" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N5" t="str">
+        <v/>
+      </c>
+      <c r="O5" t="str">
+        <v/>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
         <v/>
       </c>
     </row>
@@ -632,12 +712,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J6" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K6" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L6" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M6" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N6" t="str">
+        <v/>
+      </c>
+      <c r="O6" t="str">
+        <v/>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
         <v/>
       </c>
     </row>
@@ -670,12 +765,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J7" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K7" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L7" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M7" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N7" t="str">
+        <v/>
+      </c>
+      <c r="O7" t="str">
+        <v/>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
         <v/>
       </c>
     </row>
@@ -708,12 +818,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J8" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K8" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L8" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M8" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N8" t="str">
+        <v/>
+      </c>
+      <c r="O8" t="str">
+        <v/>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
         <v/>
       </c>
     </row>
@@ -746,12 +871,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J9" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K9" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L9" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M9" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N9" t="str">
+        <v/>
+      </c>
+      <c r="O9" t="str">
+        <v/>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
         <v/>
       </c>
     </row>
@@ -784,12 +924,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J10" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K10" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L10" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M10" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N10" t="str">
+        <v/>
+      </c>
+      <c r="O10" t="str">
+        <v/>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
         <v/>
       </c>
     </row>
@@ -822,12 +977,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J11" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K11" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L11" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M11" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N11" t="str">
+        <v/>
+      </c>
+      <c r="O11" t="str">
+        <v/>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
         <v/>
       </c>
     </row>
@@ -860,12 +1030,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J12" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K12" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L12" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M12" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N12" t="str">
+        <v/>
+      </c>
+      <c r="O12" t="str">
+        <v/>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
         <v/>
       </c>
     </row>
@@ -898,12 +1083,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J13" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K13" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L13" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M13" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N13" t="str">
+        <v/>
+      </c>
+      <c r="O13" t="str">
+        <v/>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
         <v/>
       </c>
     </row>
@@ -936,12 +1136,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K14" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L14" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M14" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N14" t="str">
+        <v/>
+      </c>
+      <c r="O14" t="str">
+        <v/>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
         <v/>
       </c>
     </row>
@@ -974,12 +1189,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J15" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K15" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L15" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M15" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N15" t="str">
+        <v/>
+      </c>
+      <c r="O15" t="str">
+        <v/>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
         <v/>
       </c>
     </row>
@@ -1012,12 +1242,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J16" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K16" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L16" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M16" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N16" t="str">
+        <v/>
+      </c>
+      <c r="O16" t="str">
+        <v/>
+      </c>
+      <c r="P16" t="str">
+        <v/>
+      </c>
+      <c r="Q16" t="str">
         <v/>
       </c>
     </row>
@@ -1050,12 +1295,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J17" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K17" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L17" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M17" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N17" t="str">
+        <v/>
+      </c>
+      <c r="O17" t="str">
+        <v/>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
         <v>Also has location at 17 East Main Street, Walla Walla, WA 99362</v>
       </c>
     </row>
@@ -1088,12 +1348,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J18" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K18" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L18" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M18" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N18" t="str">
+        <v/>
+      </c>
+      <c r="O18" t="str">
+        <v/>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
         <v/>
       </c>
     </row>
@@ -1126,12 +1401,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J19" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K19" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L19" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M19" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N19" t="str">
+        <v/>
+      </c>
+      <c r="O19" t="str">
+        <v/>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
         <v/>
       </c>
     </row>
@@ -1164,12 +1454,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J20" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K20" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L20" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N20" t="str">
+        <v/>
+      </c>
+      <c r="O20" t="str">
+        <v/>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
         <v/>
       </c>
     </row>
@@ -1202,12 +1507,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J21" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K21" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L21" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M21" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N21" t="str">
+        <v/>
+      </c>
+      <c r="O21" t="str">
+        <v/>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
         <v/>
       </c>
     </row>
@@ -1240,12 +1560,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J22" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K22" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L22" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M22" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N22" t="str">
+        <v/>
+      </c>
+      <c r="O22" t="str">
+        <v/>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
         <v/>
       </c>
     </row>
@@ -1278,12 +1613,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J23" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K23" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L23" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M23" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N23" t="str">
+        <v/>
+      </c>
+      <c r="O23" t="str">
+        <v/>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
         <v/>
       </c>
     </row>
@@ -1316,12 +1666,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J24" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K24" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L24" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M24" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N24" t="str">
+        <v/>
+      </c>
+      <c r="O24" t="str">
+        <v/>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
         <v/>
       </c>
     </row>
@@ -1354,12 +1719,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J25" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K25" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L25" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N25" t="str">
+        <v/>
+      </c>
+      <c r="O25" t="str">
+        <v/>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
         <v/>
       </c>
     </row>
@@ -1392,12 +1772,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J26" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K26" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L26" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M26" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N26" t="str">
+        <v/>
+      </c>
+      <c r="O26" t="str">
+        <v/>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
         <v/>
       </c>
     </row>
@@ -1430,12 +1825,27 @@
         <v>Walla Walla Valley - Airport</v>
       </c>
       <c r="J27" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K27" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L27" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M27" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N27" t="str">
+        <v/>
+      </c>
+      <c r="O27" t="str">
+        <v/>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
         <v/>
       </c>
     </row>
@@ -1468,12 +1878,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J28" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K28" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L28" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M28" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N28" t="str">
+        <v/>
+      </c>
+      <c r="O28" t="str">
+        <v/>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
         <v/>
       </c>
     </row>
@@ -1506,12 +1931,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J29" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K29" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L29" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M29" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N29" t="str">
+        <v/>
+      </c>
+      <c r="O29" t="str">
+        <v/>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
         <v/>
       </c>
     </row>
@@ -1544,12 +1984,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J30" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K30" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L30" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M30" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N30" t="str">
+        <v/>
+      </c>
+      <c r="O30" t="str">
+        <v/>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
         <v/>
       </c>
     </row>
@@ -1582,12 +2037,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J31" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K31" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L31" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M31" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N31" t="str">
+        <v/>
+      </c>
+      <c r="O31" t="str">
+        <v/>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
         <v/>
       </c>
     </row>
@@ -1620,12 +2090,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J32" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K32" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L32" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M32" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N32" t="str">
+        <v/>
+      </c>
+      <c r="O32" t="str">
+        <v/>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
         <v/>
       </c>
     </row>
@@ -1658,12 +2143,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J33" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K33" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L33" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M33" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N33" t="str">
+        <v/>
+      </c>
+      <c r="O33" t="str">
+        <v/>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
         <v/>
       </c>
     </row>
@@ -1696,12 +2196,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J34" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K34" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L34" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M34" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N34" t="str">
+        <v/>
+      </c>
+      <c r="O34" t="str">
+        <v/>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
         <v/>
       </c>
     </row>
@@ -1734,12 +2249,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J35" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K35" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L35" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M35" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N35" t="str">
+        <v/>
+      </c>
+      <c r="O35" t="str">
+        <v/>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
         <v/>
       </c>
     </row>
@@ -1772,12 +2302,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J36" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K36" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L36" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M36" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N36" t="str">
+        <v/>
+      </c>
+      <c r="O36" t="str">
+        <v/>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
         <v/>
       </c>
     </row>
@@ -1810,12 +2355,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J37" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K37" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L37" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M37" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N37" t="str">
+        <v/>
+      </c>
+      <c r="O37" t="str">
+        <v/>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
         <v/>
       </c>
     </row>
@@ -1848,12 +2408,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J38" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K38" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L38" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M38" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N38" t="str">
+        <v/>
+      </c>
+      <c r="O38" t="str">
+        <v/>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
         <v/>
       </c>
     </row>
@@ -1886,12 +2461,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J39" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K39" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L39" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M39" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N39" t="str">
+        <v/>
+      </c>
+      <c r="O39" t="str">
+        <v/>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
         <v/>
       </c>
     </row>
@@ -1924,12 +2514,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J40" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K40" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L40" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M40" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N40" t="str">
+        <v/>
+      </c>
+      <c r="O40" t="str">
+        <v/>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
         <v/>
       </c>
     </row>
@@ -1962,12 +2567,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J41" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K41" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L41" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M41" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N41" t="str">
+        <v/>
+      </c>
+      <c r="O41" t="str">
+        <v/>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
         <v/>
       </c>
     </row>
@@ -2000,12 +2620,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J42" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K42" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L42" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M42" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N42" t="str">
+        <v/>
+      </c>
+      <c r="O42" t="str">
+        <v/>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
         <v/>
       </c>
     </row>
@@ -2038,13 +2673,28 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J43" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Syrah, Pinot Noir, Cabernet Franc, Mourvèdre, Rosé, Picpoul</v>
       </c>
       <c r="K43" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L43" t="str">
-        <v/>
+        <v>Varies - check website</v>
+      </c>
+      <c r="M43" t="str">
+        <v>By Appointment</v>
+      </c>
+      <c r="N43" t="str">
+        <v>https://gramercycellars.com/wp-content/uploads/2025/03/Tasting-Room-Mast-1500x900.jpg</v>
+      </c>
+      <c r="O43" t="str">
+        <v/>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v>Specializes in Rhône and Bordeaux blends</v>
       </c>
     </row>
     <row r="44">
@@ -2076,12 +2726,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J44" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K44" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L44" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M44" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N44" t="str">
+        <v/>
+      </c>
+      <c r="O44" t="str">
+        <v/>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
         <v/>
       </c>
     </row>
@@ -2114,12 +2779,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J45" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K45" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L45" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M45" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N45" t="str">
+        <v/>
+      </c>
+      <c r="O45" t="str">
+        <v/>
+      </c>
+      <c r="P45" t="str">
+        <v/>
+      </c>
+      <c r="Q45" t="str">
         <v/>
       </c>
     </row>
@@ -2152,12 +2832,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J46" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K46" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L46" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M46" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N46" t="str">
+        <v/>
+      </c>
+      <c r="O46" t="str">
+        <v/>
+      </c>
+      <c r="P46" t="str">
+        <v/>
+      </c>
+      <c r="Q46" t="str">
         <v/>
       </c>
     </row>
@@ -2190,12 +2885,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J47" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K47" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L47" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M47" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N47" t="str">
+        <v/>
+      </c>
+      <c r="O47" t="str">
+        <v/>
+      </c>
+      <c r="P47" t="str">
+        <v/>
+      </c>
+      <c r="Q47" t="str">
         <v/>
       </c>
     </row>
@@ -2228,12 +2938,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J48" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K48" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L48" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M48" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N48" t="str">
+        <v/>
+      </c>
+      <c r="O48" t="str">
+        <v/>
+      </c>
+      <c r="P48" t="str">
+        <v/>
+      </c>
+      <c r="Q48" t="str">
         <v/>
       </c>
     </row>
@@ -2266,12 +2991,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J49" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K49" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L49" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M49" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N49" t="str">
+        <v/>
+      </c>
+      <c r="O49" t="str">
+        <v/>
+      </c>
+      <c r="P49" t="str">
+        <v/>
+      </c>
+      <c r="Q49" t="str">
         <v/>
       </c>
     </row>
@@ -2304,12 +3044,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J50" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K50" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L50" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M50" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N50" t="str">
+        <v/>
+      </c>
+      <c r="O50" t="str">
+        <v/>
+      </c>
+      <c r="P50" t="str">
+        <v/>
+      </c>
+      <c r="Q50" t="str">
         <v/>
       </c>
     </row>
@@ -2342,12 +3097,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J51" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K51" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L51" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M51" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N51" t="str">
+        <v/>
+      </c>
+      <c r="O51" t="str">
+        <v/>
+      </c>
+      <c r="P51" t="str">
+        <v/>
+      </c>
+      <c r="Q51" t="str">
         <v/>
       </c>
     </row>
@@ -2380,12 +3150,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J52" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K52" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L52" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M52" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N52" t="str">
+        <v/>
+      </c>
+      <c r="O52" t="str">
+        <v/>
+      </c>
+      <c r="P52" t="str">
+        <v/>
+      </c>
+      <c r="Q52" t="str">
         <v/>
       </c>
     </row>
@@ -2418,12 +3203,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J53" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K53" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L53" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M53" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N53" t="str">
+        <v/>
+      </c>
+      <c r="O53" t="str">
+        <v/>
+      </c>
+      <c r="P53" t="str">
+        <v/>
+      </c>
+      <c r="Q53" t="str">
         <v/>
       </c>
     </row>
@@ -2456,12 +3256,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J54" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K54" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L54" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M54" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N54" t="str">
+        <v/>
+      </c>
+      <c r="O54" t="str">
+        <v/>
+      </c>
+      <c r="P54" t="str">
+        <v/>
+      </c>
+      <c r="Q54" t="str">
         <v/>
       </c>
     </row>
@@ -2494,12 +3309,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J55" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K55" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L55" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M55" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N55" t="str">
+        <v/>
+      </c>
+      <c r="O55" t="str">
+        <v/>
+      </c>
+      <c r="P55" t="str">
+        <v/>
+      </c>
+      <c r="Q55" t="str">
         <v/>
       </c>
     </row>
@@ -2532,12 +3362,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J56" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K56" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L56" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M56" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N56" t="str">
+        <v/>
+      </c>
+      <c r="O56" t="str">
+        <v/>
+      </c>
+      <c r="P56" t="str">
+        <v/>
+      </c>
+      <c r="Q56" t="str">
         <v/>
       </c>
     </row>
@@ -2570,12 +3415,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J57" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K57" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L57" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M57" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N57" t="str">
+        <v/>
+      </c>
+      <c r="O57" t="str">
+        <v/>
+      </c>
+      <c r="P57" t="str">
+        <v/>
+      </c>
+      <c r="Q57" t="str">
         <v/>
       </c>
     </row>
@@ -2608,12 +3468,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J58" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K58" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L58" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M58" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N58" t="str">
+        <v/>
+      </c>
+      <c r="O58" t="str">
+        <v/>
+      </c>
+      <c r="P58" t="str">
+        <v/>
+      </c>
+      <c r="Q58" t="str">
         <v/>
       </c>
     </row>
@@ -2646,12 +3521,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J59" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K59" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L59" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M59" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N59" t="str">
+        <v/>
+      </c>
+      <c r="O59" t="str">
+        <v/>
+      </c>
+      <c r="P59" t="str">
+        <v/>
+      </c>
+      <c r="Q59" t="str">
         <v/>
       </c>
     </row>
@@ -2684,12 +3574,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J60" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K60" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L60" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M60" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N60" t="str">
+        <v/>
+      </c>
+      <c r="O60" t="str">
+        <v/>
+      </c>
+      <c r="P60" t="str">
+        <v/>
+      </c>
+      <c r="Q60" t="str">
         <v/>
       </c>
     </row>
@@ -2722,12 +3627,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J61" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K61" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L61" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M61" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N61" t="str">
+        <v/>
+      </c>
+      <c r="O61" t="str">
+        <v/>
+      </c>
+      <c r="P61" t="str">
+        <v/>
+      </c>
+      <c r="Q61" t="str">
         <v/>
       </c>
     </row>
@@ -2760,12 +3680,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J62" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K62" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L62" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M62" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N62" t="str">
+        <v/>
+      </c>
+      <c r="O62" t="str">
+        <v/>
+      </c>
+      <c r="P62" t="str">
+        <v/>
+      </c>
+      <c r="Q62" t="str">
         <v/>
       </c>
     </row>
@@ -2798,12 +3733,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J63" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K63" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L63" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M63" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N63" t="str">
+        <v/>
+      </c>
+      <c r="O63" t="str">
+        <v/>
+      </c>
+      <c r="P63" t="str">
+        <v/>
+      </c>
+      <c r="Q63" t="str">
         <v/>
       </c>
     </row>
@@ -2836,12 +3786,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J64" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K64" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L64" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M64" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N64" t="str">
+        <v/>
+      </c>
+      <c r="O64" t="str">
+        <v/>
+      </c>
+      <c r="P64" t="str">
+        <v/>
+      </c>
+      <c r="Q64" t="str">
         <v/>
       </c>
     </row>
@@ -2874,12 +3839,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J65" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K65" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L65" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M65" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N65" t="str">
+        <v/>
+      </c>
+      <c r="O65" t="str">
+        <v/>
+      </c>
+      <c r="P65" t="str">
+        <v/>
+      </c>
+      <c r="Q65" t="str">
         <v/>
       </c>
     </row>
@@ -2912,12 +3892,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J66" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K66" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L66" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M66" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N66" t="str">
+        <v/>
+      </c>
+      <c r="O66" t="str">
+        <v/>
+      </c>
+      <c r="P66" t="str">
+        <v/>
+      </c>
+      <c r="Q66" t="str">
         <v/>
       </c>
     </row>
@@ -2950,12 +3945,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J67" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K67" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L67" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M67" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N67" t="str">
+        <v/>
+      </c>
+      <c r="O67" t="str">
+        <v/>
+      </c>
+      <c r="P67" t="str">
+        <v/>
+      </c>
+      <c r="Q67" t="str">
         <v/>
       </c>
     </row>
@@ -2988,12 +3998,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J68" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K68" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L68" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M68" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N68" t="str">
+        <v/>
+      </c>
+      <c r="O68" t="str">
+        <v/>
+      </c>
+      <c r="P68" t="str">
+        <v/>
+      </c>
+      <c r="Q68" t="str">
         <v/>
       </c>
     </row>
@@ -3026,12 +4051,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J69" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K69" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L69" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M69" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N69" t="str">
+        <v/>
+      </c>
+      <c r="O69" t="str">
+        <v/>
+      </c>
+      <c r="P69" t="str">
+        <v/>
+      </c>
+      <c r="Q69" t="str">
         <v/>
       </c>
     </row>
@@ -3064,12 +4104,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J70" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K70" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L70" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M70" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N70" t="str">
+        <v/>
+      </c>
+      <c r="O70" t="str">
+        <v/>
+      </c>
+      <c r="P70" t="str">
+        <v/>
+      </c>
+      <c r="Q70" t="str">
         <v/>
       </c>
     </row>
@@ -3102,12 +4157,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J71" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K71" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L71" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M71" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N71" t="str">
+        <v/>
+      </c>
+      <c r="O71" t="str">
+        <v/>
+      </c>
+      <c r="P71" t="str">
+        <v/>
+      </c>
+      <c r="Q71" t="str">
         <v/>
       </c>
     </row>
@@ -3140,12 +4210,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J72" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K72" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L72" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M72" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N72" t="str">
+        <v/>
+      </c>
+      <c r="O72" t="str">
+        <v/>
+      </c>
+      <c r="P72" t="str">
+        <v/>
+      </c>
+      <c r="Q72" t="str">
         <v/>
       </c>
     </row>
@@ -3178,12 +4263,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J73" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K73" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L73" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M73" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N73" t="str">
+        <v/>
+      </c>
+      <c r="O73" t="str">
+        <v/>
+      </c>
+      <c r="P73" t="str">
+        <v/>
+      </c>
+      <c r="Q73" t="str">
         <v/>
       </c>
     </row>
@@ -3216,13 +4316,28 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J74" t="str">
-        <v/>
+        <v>Merlot, Cabernet Sauvignon</v>
       </c>
       <c r="K74" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L74" t="str">
-        <v/>
+        <v>Varies - check website</v>
+      </c>
+      <c r="M74" t="str">
+        <v>Private Seated Tastings</v>
+      </c>
+      <c r="N74" t="str">
+        <v>https://sevenhillswinery.com/wp-content/uploads/2023/05/Seven-Hills-Winery-Pentad-Tasting-Room.png</v>
+      </c>
+      <c r="O74" t="str">
+        <v/>
+      </c>
+      <c r="P74" t="str">
+        <v/>
+      </c>
+      <c r="Q74" t="str">
+        <v>Downtown Walla Walla's only historic working winemaking facility, established 1988</v>
       </c>
     </row>
     <row r="75">
@@ -3254,12 +4369,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J75" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K75" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L75" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M75" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N75" t="str">
+        <v/>
+      </c>
+      <c r="O75" t="str">
+        <v/>
+      </c>
+      <c r="P75" t="str">
+        <v/>
+      </c>
+      <c r="Q75" t="str">
         <v/>
       </c>
     </row>
@@ -3292,12 +4422,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J76" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K76" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L76" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M76" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N76" t="str">
+        <v/>
+      </c>
+      <c r="O76" t="str">
+        <v/>
+      </c>
+      <c r="P76" t="str">
+        <v/>
+      </c>
+      <c r="Q76" t="str">
         <v/>
       </c>
     </row>
@@ -3330,12 +4475,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J77" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K77" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L77" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M77" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N77" t="str">
+        <v/>
+      </c>
+      <c r="O77" t="str">
+        <v/>
+      </c>
+      <c r="P77" t="str">
+        <v/>
+      </c>
+      <c r="Q77" t="str">
         <v/>
       </c>
     </row>
@@ -3368,12 +4528,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J78" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K78" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L78" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M78" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N78" t="str">
+        <v/>
+      </c>
+      <c r="O78" t="str">
+        <v/>
+      </c>
+      <c r="P78" t="str">
+        <v/>
+      </c>
+      <c r="Q78" t="str">
         <v/>
       </c>
     </row>
@@ -3406,12 +4581,27 @@
         <v>Walla Walla Valley - Airport</v>
       </c>
       <c r="J79" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K79" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L79" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M79" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N79" t="str">
+        <v/>
+      </c>
+      <c r="O79" t="str">
+        <v/>
+      </c>
+      <c r="P79" t="str">
+        <v/>
+      </c>
+      <c r="Q79" t="str">
         <v/>
       </c>
     </row>
@@ -3444,12 +4634,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J80" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K80" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L80" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M80" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N80" t="str">
+        <v/>
+      </c>
+      <c r="O80" t="str">
+        <v/>
+      </c>
+      <c r="P80" t="str">
+        <v/>
+      </c>
+      <c r="Q80" t="str">
         <v/>
       </c>
     </row>
@@ -3482,12 +4687,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J81" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K81" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L81" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M81" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N81" t="str">
+        <v/>
+      </c>
+      <c r="O81" t="str">
+        <v/>
+      </c>
+      <c r="P81" t="str">
+        <v/>
+      </c>
+      <c r="Q81" t="str">
         <v/>
       </c>
     </row>
@@ -3520,12 +4740,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J82" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K82" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L82" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M82" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N82" t="str">
+        <v/>
+      </c>
+      <c r="O82" t="str">
+        <v/>
+      </c>
+      <c r="P82" t="str">
+        <v/>
+      </c>
+      <c r="Q82" t="str">
         <v/>
       </c>
     </row>
@@ -3558,12 +4793,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J83" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K83" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L83" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M83" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N83" t="str">
+        <v/>
+      </c>
+      <c r="O83" t="str">
+        <v/>
+      </c>
+      <c r="P83" t="str">
+        <v/>
+      </c>
+      <c r="Q83" t="str">
         <v/>
       </c>
     </row>
@@ -3596,12 +4846,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J84" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K84" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L84" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M84" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N84" t="str">
+        <v/>
+      </c>
+      <c r="O84" t="str">
+        <v/>
+      </c>
+      <c r="P84" t="str">
+        <v/>
+      </c>
+      <c r="Q84" t="str">
         <v/>
       </c>
     </row>
@@ -3634,12 +4899,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J85" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K85" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L85" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M85" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N85" t="str">
+        <v/>
+      </c>
+      <c r="O85" t="str">
+        <v/>
+      </c>
+      <c r="P85" t="str">
+        <v/>
+      </c>
+      <c r="Q85" t="str">
         <v/>
       </c>
     </row>
@@ -3672,12 +4952,27 @@
         <v>Walla Walla Valley - Downtown</v>
       </c>
       <c r="J86" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K86" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L86" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M86" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N86" t="str">
+        <v/>
+      </c>
+      <c r="O86" t="str">
+        <v/>
+      </c>
+      <c r="P86" t="str">
+        <v/>
+      </c>
+      <c r="Q86" t="str">
         <v/>
       </c>
     </row>
@@ -3710,12 +5005,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J87" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K87" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L87" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M87" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N87" t="str">
+        <v/>
+      </c>
+      <c r="O87" t="str">
+        <v/>
+      </c>
+      <c r="P87" t="str">
+        <v/>
+      </c>
+      <c r="Q87" t="str">
         <v/>
       </c>
     </row>
@@ -3748,12 +5058,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J88" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K88" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L88" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M88" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N88" t="str">
+        <v/>
+      </c>
+      <c r="O88" t="str">
+        <v/>
+      </c>
+      <c r="P88" t="str">
+        <v/>
+      </c>
+      <c r="Q88" t="str">
         <v/>
       </c>
     </row>
@@ -3786,12 +5111,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J89" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K89" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L89" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M89" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N89" t="str">
+        <v/>
+      </c>
+      <c r="O89" t="str">
+        <v/>
+      </c>
+      <c r="P89" t="str">
+        <v/>
+      </c>
+      <c r="Q89" t="str">
         <v/>
       </c>
     </row>
@@ -3824,12 +5164,27 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J90" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K90" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L90" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M90" t="str">
+        <v>By Appointment/Reservation</v>
+      </c>
+      <c r="N90" t="str">
+        <v/>
+      </c>
+      <c r="O90" t="str">
+        <v/>
+      </c>
+      <c r="P90" t="str">
+        <v/>
+      </c>
+      <c r="Q90" t="str">
         <v/>
       </c>
     </row>
@@ -3862,12 +5217,27 @@
         <v>Walla Walla Valley</v>
       </c>
       <c r="J91" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K91" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L91" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M91" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N91" t="str">
+        <v/>
+      </c>
+      <c r="O91" t="str">
+        <v/>
+      </c>
+      <c r="P91" t="str">
+        <v/>
+      </c>
+      <c r="Q91" t="str">
         <v/>
       </c>
     </row>
@@ -3900,18 +5270,33 @@
         <v>The Rocks District of Milton-Freewater</v>
       </c>
       <c r="J92" t="str">
-        <v/>
+        <v>Cabernet Sauvignon, Merlot, Syrah (typical Walla Walla)</v>
       </c>
       <c r="K92" t="str">
-        <v/>
+        <v>Contact winery for hours</v>
       </c>
       <c r="L92" t="str">
+        <v>Varies - check website</v>
+      </c>
+      <c r="M92" t="str">
+        <v>Contact for details</v>
+      </c>
+      <c r="N92" t="str">
+        <v/>
+      </c>
+      <c r="O92" t="str">
+        <v/>
+      </c>
+      <c r="P92" t="str">
+        <v/>
+      </c>
+      <c r="Q92" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L92"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q92"/>
   </ignoredErrors>
 </worksheet>
 </file>